--- a/Dependencies/Ping_2018/percent_validated_genomehomol_SAAP.xlsx
+++ b/Dependencies/Ping_2018/percent_validated_genomehomol_SAAP.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>39.09090909090909</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61.80371352785146</v>
+        <v>38.82618510158014</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51.62162162162161</v>
+        <v>35.63218390804598</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57.20164609053497</v>
+        <v>33.45588235294117</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61.53846153846154</v>
+        <v>41.19718309859155</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -571,16 +571,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fcb2</t>
+          <t>fcb1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>58.26771653543307</v>
+        <v>29.4314381270903</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -594,16 +594,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fcb3</t>
+          <t>fcb2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56.03448275862068</v>
+        <v>24.84472049689441</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -617,16 +617,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fcb4</t>
+          <t>fcb3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63.07692307692307</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -640,18 +640,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>fcb4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>32.91139240506329</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Validated SAAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>fcb5</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>51.40845070422535</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D11" t="n">
+        <v>21.21212121212121</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Validated SAAP</t>
         </is>

--- a/Dependencies/Ping_2018/percent_validated_genomehomol_SAAP.xlsx
+++ b/Dependencies/Ping_2018/percent_validated_genomehomol_SAAP.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39.09090909090909</v>
+        <v>53.63636363636364</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>38.82618510158014</v>
+        <v>53.95033860045147</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.63218390804598</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33.45588235294117</v>
+        <v>52.57352941176471</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>41.19718309859155</v>
+        <v>54.92957746478874</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.4314381270903</v>
+        <v>39.46488294314381</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.84472049689441</v>
+        <v>46.58385093167702</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26.31578947368421</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32.91139240506329</v>
+        <v>48.52320675105485</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.21212121212121</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
